--- a/Squad-Planner.xlsx
+++ b/Squad-Planner.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\asus\Documents\GitHub\FC-Squad-Planner\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\asus\Documents\GitHub\FC-Squad-List\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F05882F8-788C-4624-AFEF-1A9F32F60B37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C02FF8C-1DF7-4896-8658-59091C840575}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{795DECCB-EE4C-4F5D-BCE1-865E97697E04}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="42">
   <si>
     <t>Built for FC26</t>
   </si>
@@ -59,25 +59,112 @@
     <t>X</t>
   </si>
   <si>
-    <t>/ X (max)</t>
-  </si>
-  <si>
-    <t>Homegrown in Nation</t>
-  </si>
-  <si>
-    <t>Homegrown at Club</t>
-  </si>
-  <si>
     <t>Foreign Players</t>
   </si>
   <si>
-    <t>/ X (min)</t>
-  </si>
-  <si>
     <t>FC Squad Planner dashboard developed by Matthew Emerson.</t>
   </si>
   <si>
     <t>None Selected</t>
+  </si>
+  <si>
+    <t>Squad Statistics</t>
+  </si>
+  <si>
+    <t>(max)</t>
+  </si>
+  <si>
+    <t>/ X</t>
+  </si>
+  <si>
+    <t>Nation</t>
+  </si>
+  <si>
+    <t>Homegrown in</t>
+  </si>
+  <si>
+    <t>Homegrown at</t>
+  </si>
+  <si>
+    <t>Club</t>
+  </si>
+  <si>
+    <t>Total Players</t>
+  </si>
+  <si>
+    <t>Average Age</t>
+  </si>
+  <si>
+    <t>Average Rating</t>
+  </si>
+  <si>
+    <t>Average Potential</t>
+  </si>
+  <si>
+    <t>X.XX</t>
+  </si>
+  <si>
+    <t>XX.X</t>
+  </si>
+  <si>
+    <t>Overall</t>
+  </si>
+  <si>
+    <t>Goalkeepers</t>
+  </si>
+  <si>
+    <t>Defenders</t>
+  </si>
+  <si>
+    <t>Midfielders</t>
+  </si>
+  <si>
+    <t>Attackers</t>
+  </si>
+  <si>
+    <t>XX</t>
+  </si>
+  <si>
+    <t>Position Groups</t>
+  </si>
+  <si>
+    <t>Squad Roles</t>
+  </si>
+  <si>
+    <t>Crucial</t>
+  </si>
+  <si>
+    <t>Important</t>
+  </si>
+  <si>
+    <t>Rotation</t>
+  </si>
+  <si>
+    <t>Sporadic</t>
+  </si>
+  <si>
+    <t>Prospect</t>
+  </si>
+  <si>
+    <t>Financial</t>
+  </si>
+  <si>
+    <t>£ XX.X k</t>
+  </si>
+  <si>
+    <t>Total Value</t>
+  </si>
+  <si>
+    <t>Average Wage (pw)</t>
+  </si>
+  <si>
+    <t>£ XXX.X m</t>
+  </si>
+  <si>
+    <t>Unique Nationalities</t>
+  </si>
+  <si>
+    <t>Loaned Out Players</t>
   </si>
 </sst>
 </file>
@@ -205,7 +292,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="19">
+  <borders count="22">
     <border>
       <left/>
       <right/>
@@ -397,8 +484,35 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="double">
+        <color theme="2" tint="-0.499984740745262"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color theme="2" tint="-0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FF2B0B27"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="10">
+  <cellStyleXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0"/>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -418,7 +532,7 @@
     <xf numFmtId="0" fontId="11" fillId="4" borderId="8" applyNumberFormat="0" applyProtection="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="5" fillId="4" borderId="0" applyBorder="0">
+    <xf numFmtId="1" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="4" borderId="0" applyNumberFormat="0">
@@ -427,95 +541,150 @@
     <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0">
+      <alignment horizontal="right" vertical="center" textRotation="90"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="3" xfId="9" applyBorder="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="13" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="2">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="0" xfId="5" applyBorder="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="17" xfId="3" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="4" xfId="1" applyBorder="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="3" xfId="1" applyBorder="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="8">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="1" applyBorder="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="4" borderId="8" xfId="6">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="8">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="5" fillId="4" borderId="4" xfId="7" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="3" xfId="9" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="8" fillId="4" borderId="0" xfId="9" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="4" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="3" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="21" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="5" fillId="4" borderId="0" xfId="7">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="5" fillId="4" borderId="0" xfId="7" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="5" fillId="4" borderId="0" xfId="7" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="12" xfId="10" applyBorder="1">
+      <alignment horizontal="right" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="12" xfId="10" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="12" xfId="10" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="1" fontId="5" fillId="4" borderId="0" xfId="7" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="13" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="2">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="0" xfId="5" applyBorder="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="1" applyBorder="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="4" xfId="1" applyBorder="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="3" xfId="1" applyBorder="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="5" fillId="4" borderId="4" xfId="7" applyBorder="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="17" xfId="3" applyAlignment="1"/>
   </cellXfs>
-  <cellStyles count="10">
+  <cellStyles count="11">
     <cellStyle name="Explanatory Text" xfId="9" builtinId="53" customBuiltin="1"/>
     <cellStyle name="Heading 1" xfId="2" builtinId="16" customBuiltin="1"/>
     <cellStyle name="Heading 2" xfId="3" builtinId="17" customBuiltin="1"/>
@@ -525,15 +694,16 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" customBuiltin="1"/>
     <cellStyle name="Note" xfId="8" builtinId="10" customBuiltin="1"/>
     <cellStyle name="Output" xfId="7" builtinId="21" customBuiltin="1"/>
+    <cellStyle name="Sideways Label" xfId="10" xr:uid="{081C747B-EBB3-4313-9175-C0B689E48230}"/>
     <cellStyle name="Title" xfId="1" builtinId="15" customBuiltin="1"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FF2B0B27"/>
       <color rgb="FF8C2681"/>
       <color rgb="FF230B27"/>
-      <color rgb="FF2B0B27"/>
     </mruColors>
   </colors>
   <extLst>
@@ -864,389 +1034,953 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{39983D28-02FA-4B1E-9AB1-37FBAB16E9C5}">
-  <dimension ref="A1:U38"/>
+  <dimension ref="A1:Y43"/>
   <sheetFormatPr defaultColWidth="0" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="3.1796875" style="2" customWidth="1"/>
-    <col min="2" max="2" width="3.6328125" style="2" customWidth="1"/>
-    <col min="3" max="4" width="12.6328125" style="2" customWidth="1"/>
-    <col min="5" max="6" width="8.81640625" style="2" customWidth="1"/>
-    <col min="7" max="8" width="12.6328125" style="2" customWidth="1"/>
-    <col min="9" max="10" width="8.81640625" style="2" customWidth="1"/>
-    <col min="11" max="12" width="12.6328125" style="2" customWidth="1"/>
-    <col min="13" max="14" width="8.81640625" style="2" customWidth="1"/>
-    <col min="15" max="16" width="12.6328125" style="2" customWidth="1"/>
-    <col min="17" max="17" width="3.6328125" style="2" customWidth="1"/>
-    <col min="18" max="18" width="3.1796875" style="2" customWidth="1"/>
-    <col min="19" max="21" width="0" style="2" hidden="1"/>
-    <col min="22" max="16384" width="8.7265625" style="2" hidden="1"/>
+    <col min="1" max="1" width="6.6328125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="7.6328125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="9.6328125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="5.1796875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="9.6328125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="14.1796875" style="1" customWidth="1"/>
+    <col min="7" max="7" width="9.6328125" style="1" customWidth="1"/>
+    <col min="8" max="8" width="5.1796875" style="1" customWidth="1"/>
+    <col min="9" max="9" width="9.6328125" style="1" customWidth="1"/>
+    <col min="10" max="10" width="14.1796875" style="1" customWidth="1"/>
+    <col min="11" max="11" width="9.6328125" style="1" customWidth="1"/>
+    <col min="12" max="12" width="5.1796875" style="1" customWidth="1"/>
+    <col min="13" max="13" width="9.6328125" style="1" customWidth="1"/>
+    <col min="14" max="14" width="14.1796875" style="1" customWidth="1"/>
+    <col min="15" max="15" width="9.6328125" style="1" customWidth="1"/>
+    <col min="16" max="16" width="5.1796875" style="1" customWidth="1"/>
+    <col min="17" max="17" width="9.6328125" style="1" customWidth="1"/>
+    <col min="18" max="18" width="7.6328125" style="1" customWidth="1"/>
+    <col min="19" max="19" width="6.6328125" style="1" customWidth="1"/>
+    <col min="20" max="22" width="0" style="1" hidden="1" customWidth="1"/>
+    <col min="23" max="25" width="0" style="1" hidden="1"/>
+    <col min="26" max="16384" width="8.7265625" style="1" hidden="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:17" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="2" spans="2:17" ht="15" thickTop="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="14"/>
-      <c r="C2" s="15"/>
-      <c r="D2" s="15"/>
-      <c r="E2" s="15"/>
-      <c r="F2" s="15"/>
-      <c r="G2" s="15"/>
-      <c r="H2" s="15"/>
-      <c r="I2" s="15"/>
-      <c r="J2" s="15"/>
-      <c r="K2" s="15"/>
-      <c r="L2" s="15"/>
-      <c r="M2" s="15"/>
-      <c r="N2" s="15"/>
-      <c r="O2" s="15"/>
-      <c r="P2" s="15"/>
-      <c r="Q2" s="16"/>
-    </row>
-    <row r="3" spans="2:17" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="B3" s="17"/>
-      <c r="C3" s="25" t="s">
+    <row r="1" spans="2:18" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="2" spans="2:18" ht="15" thickTop="1" x14ac:dyDescent="0.35">
+      <c r="B2" s="8"/>
+      <c r="C2" s="9"/>
+      <c r="D2" s="9"/>
+      <c r="E2" s="9"/>
+      <c r="F2" s="9"/>
+      <c r="G2" s="9"/>
+      <c r="H2" s="9"/>
+      <c r="I2" s="9"/>
+      <c r="J2" s="9"/>
+      <c r="K2" s="9"/>
+      <c r="L2" s="9"/>
+      <c r="M2" s="9"/>
+      <c r="N2" s="9"/>
+      <c r="O2" s="9"/>
+      <c r="P2" s="9"/>
+      <c r="Q2" s="9"/>
+      <c r="R2" s="10"/>
+    </row>
+    <row r="3" spans="2:18" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="B3" s="11"/>
+      <c r="C3" s="19" t="s">
         <v>0</v>
       </c>
-      <c r="D3" s="6"/>
-      <c r="E3" s="6"/>
-      <c r="F3" s="6"/>
-      <c r="G3" s="6"/>
-      <c r="H3" s="6"/>
-      <c r="I3" s="6"/>
-      <c r="J3" s="6"/>
-      <c r="K3" s="6"/>
-      <c r="L3" s="6"/>
-      <c r="M3" s="6"/>
-      <c r="N3" s="6"/>
-      <c r="O3" s="6"/>
-      <c r="P3" s="6"/>
-      <c r="Q3" s="18"/>
-    </row>
-    <row r="4" spans="2:17" ht="48" thickBot="1" x14ac:dyDescent="1.1499999999999999">
-      <c r="B4" s="17"/>
-      <c r="C4" s="24" t="s">
+      <c r="D3" s="19"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="2"/>
+      <c r="H3" s="2"/>
+      <c r="I3" s="2"/>
+      <c r="J3" s="2"/>
+      <c r="K3" s="2"/>
+      <c r="L3" s="2"/>
+      <c r="M3" s="2"/>
+      <c r="N3" s="2"/>
+      <c r="O3" s="2"/>
+      <c r="P3" s="2"/>
+      <c r="Q3" s="2"/>
+      <c r="R3" s="12"/>
+    </row>
+    <row r="4" spans="2:18" ht="48" thickBot="1" x14ac:dyDescent="1.1499999999999999">
+      <c r="B4" s="11"/>
+      <c r="C4" s="18" t="s">
         <v>1</v>
       </c>
-      <c r="D4" s="24"/>
-      <c r="E4" s="24"/>
-      <c r="F4" s="24"/>
-      <c r="G4" s="24"/>
-      <c r="H4" s="7"/>
-      <c r="I4" s="6"/>
-      <c r="J4" s="6"/>
-      <c r="K4" s="6"/>
-      <c r="L4" s="6"/>
-      <c r="M4" s="6"/>
-      <c r="N4" s="6"/>
-      <c r="O4" s="6"/>
-      <c r="P4" s="6"/>
-      <c r="Q4" s="18"/>
-    </row>
-    <row r="5" spans="2:17" ht="15" thickTop="1" x14ac:dyDescent="0.35">
-      <c r="B5" s="17"/>
-      <c r="C5" s="6"/>
-      <c r="D5" s="6"/>
-      <c r="E5" s="6"/>
-      <c r="F5" s="6"/>
-      <c r="G5" s="6"/>
-      <c r="H5" s="6"/>
-      <c r="I5" s="6"/>
-      <c r="J5" s="6"/>
-      <c r="K5" s="6"/>
-      <c r="L5" s="6"/>
-      <c r="M5" s="5" t="s">
+      <c r="D4" s="18"/>
+      <c r="E4" s="18"/>
+      <c r="F4" s="18"/>
+      <c r="G4" s="18"/>
+      <c r="H4" s="18"/>
+      <c r="I4" s="3"/>
+      <c r="J4" s="2"/>
+      <c r="K4" s="2"/>
+      <c r="L4" s="2"/>
+      <c r="M4" s="2"/>
+      <c r="N4" s="2"/>
+      <c r="O4" s="2"/>
+      <c r="P4" s="2"/>
+      <c r="Q4" s="2"/>
+      <c r="R4" s="12"/>
+    </row>
+    <row r="5" spans="2:18" ht="15" thickTop="1" x14ac:dyDescent="0.35">
+      <c r="B5" s="11"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+      <c r="F5" s="2"/>
+      <c r="G5" s="2"/>
+      <c r="H5" s="2"/>
+      <c r="I5" s="2"/>
+      <c r="J5" s="2"/>
+      <c r="K5" s="2"/>
+      <c r="L5" s="2"/>
+      <c r="M5" s="2"/>
+      <c r="N5" s="23" t="s">
+        <v>7</v>
+      </c>
+      <c r="O5" s="23"/>
+      <c r="P5" s="23"/>
+      <c r="Q5" s="23"/>
+      <c r="R5" s="12"/>
+    </row>
+    <row r="6" spans="2:18" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B6" s="13"/>
+      <c r="C6" s="14"/>
+      <c r="D6" s="14"/>
+      <c r="E6" s="14"/>
+      <c r="F6" s="14"/>
+      <c r="G6" s="14"/>
+      <c r="H6" s="14"/>
+      <c r="I6" s="14"/>
+      <c r="J6" s="14"/>
+      <c r="K6" s="14"/>
+      <c r="L6" s="14"/>
+      <c r="M6" s="14"/>
+      <c r="N6" s="14"/>
+      <c r="O6" s="14"/>
+      <c r="P6" s="14"/>
+      <c r="Q6" s="14"/>
+      <c r="R6" s="15"/>
+    </row>
+    <row r="7" spans="2:18" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="8" spans="2:18" ht="15" thickTop="1" x14ac:dyDescent="0.35">
+      <c r="B8" s="8"/>
+      <c r="C8" s="9"/>
+      <c r="D8" s="9"/>
+      <c r="E8" s="9"/>
+      <c r="F8" s="9"/>
+      <c r="G8" s="9"/>
+      <c r="H8" s="9"/>
+      <c r="I8" s="9"/>
+      <c r="J8" s="9"/>
+      <c r="K8" s="9"/>
+      <c r="L8" s="9"/>
+      <c r="M8" s="9"/>
+      <c r="N8" s="9"/>
+      <c r="O8" s="9"/>
+      <c r="P8" s="9"/>
+      <c r="Q8" s="9"/>
+      <c r="R8" s="10"/>
+    </row>
+    <row r="9" spans="2:18" ht="35" thickBot="1" x14ac:dyDescent="0.85">
+      <c r="B9" s="11"/>
+      <c r="C9" s="20" t="s">
+        <v>2</v>
+      </c>
+      <c r="D9" s="20"/>
+      <c r="E9" s="20"/>
+      <c r="F9" s="20"/>
+      <c r="G9" s="3"/>
+      <c r="H9" s="3"/>
+      <c r="I9" s="2"/>
+      <c r="J9" s="2"/>
+      <c r="K9" s="2"/>
+      <c r="L9" s="2"/>
+      <c r="M9" s="2"/>
+      <c r="N9" s="2"/>
+      <c r="O9" s="2"/>
+      <c r="P9" s="2"/>
+      <c r="Q9" s="2"/>
+      <c r="R9" s="12"/>
+    </row>
+    <row r="10" spans="2:18" ht="15" thickTop="1" x14ac:dyDescent="0.35">
+      <c r="B10" s="11"/>
+      <c r="C10" s="2"/>
+      <c r="D10" s="2"/>
+      <c r="E10" s="2"/>
+      <c r="F10" s="2"/>
+      <c r="G10" s="2"/>
+      <c r="H10" s="2"/>
+      <c r="I10" s="2"/>
+      <c r="J10" s="2"/>
+      <c r="K10" s="2"/>
+      <c r="L10" s="2"/>
+      <c r="M10" s="2"/>
+      <c r="N10" s="2"/>
+      <c r="O10" s="2"/>
+      <c r="P10" s="2"/>
+      <c r="Q10" s="2"/>
+      <c r="R10" s="12"/>
+    </row>
+    <row r="11" spans="2:18" ht="16" x14ac:dyDescent="0.35">
+      <c r="B11" s="11"/>
+      <c r="C11" s="24" t="s">
+        <v>3</v>
+      </c>
+      <c r="D11" s="24"/>
+      <c r="E11" s="24"/>
+      <c r="F11" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="G11" s="25"/>
+      <c r="H11" s="25"/>
+      <c r="I11" s="2"/>
+      <c r="J11" s="2"/>
+      <c r="K11" s="2"/>
+      <c r="L11" s="2"/>
+      <c r="M11" s="2"/>
+      <c r="N11" s="2"/>
+      <c r="O11" s="2"/>
+      <c r="P11" s="2"/>
+      <c r="Q11" s="2"/>
+      <c r="R11" s="12"/>
+    </row>
+    <row r="12" spans="2:18" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B12" s="11"/>
+      <c r="C12" s="2"/>
+      <c r="D12" s="2"/>
+      <c r="E12" s="2"/>
+      <c r="F12" s="2"/>
+      <c r="G12" s="2"/>
+      <c r="H12" s="2"/>
+      <c r="I12" s="2"/>
+      <c r="J12" s="2"/>
+      <c r="K12" s="2"/>
+      <c r="L12" s="2"/>
+      <c r="M12" s="2"/>
+      <c r="N12" s="2"/>
+      <c r="O12" s="2"/>
+      <c r="P12" s="2"/>
+      <c r="Q12" s="2"/>
+      <c r="R12" s="12"/>
+    </row>
+    <row r="13" spans="2:18" ht="7" customHeight="1" thickTop="1" x14ac:dyDescent="0.35">
+      <c r="B13" s="11"/>
+      <c r="C13" s="4"/>
+      <c r="D13" s="26"/>
+      <c r="E13" s="5"/>
+      <c r="F13" s="2"/>
+      <c r="G13" s="4"/>
+      <c r="H13" s="26"/>
+      <c r="I13" s="5"/>
+      <c r="J13" s="2"/>
+      <c r="K13" s="4"/>
+      <c r="L13" s="26"/>
+      <c r="M13" s="5"/>
+      <c r="N13" s="2"/>
+      <c r="O13" s="4"/>
+      <c r="P13" s="26"/>
+      <c r="Q13" s="5"/>
+      <c r="R13" s="12"/>
+    </row>
+    <row r="14" spans="2:18" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B14" s="11"/>
+      <c r="C14" s="21" t="s">
+        <v>4</v>
+      </c>
+      <c r="D14" s="24"/>
+      <c r="E14" s="22"/>
+      <c r="F14" s="2"/>
+      <c r="G14" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="H14" s="24"/>
+      <c r="I14" s="22"/>
+      <c r="J14" s="2"/>
+      <c r="K14" s="21" t="s">
+        <v>14</v>
+      </c>
+      <c r="L14" s="24"/>
+      <c r="M14" s="22"/>
+      <c r="N14" s="2"/>
+      <c r="O14" s="31" t="s">
+        <v>6</v>
+      </c>
+      <c r="P14" s="32"/>
+      <c r="Q14" s="33"/>
+      <c r="R14" s="12"/>
+    </row>
+    <row r="15" spans="2:18" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B15" s="11"/>
+      <c r="C15" s="21"/>
+      <c r="D15" s="24"/>
+      <c r="E15" s="22"/>
+      <c r="F15" s="2"/>
+      <c r="G15" s="21" t="s">
+        <v>12</v>
+      </c>
+      <c r="H15" s="24"/>
+      <c r="I15" s="22"/>
+      <c r="J15" s="2"/>
+      <c r="K15" s="21" t="s">
+        <v>15</v>
+      </c>
+      <c r="L15" s="24"/>
+      <c r="M15" s="22"/>
+      <c r="N15" s="2"/>
+      <c r="O15" s="31"/>
+      <c r="P15" s="32"/>
+      <c r="Q15" s="33"/>
+      <c r="R15" s="16"/>
+    </row>
+    <row r="16" spans="2:18" ht="28" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B16" s="11"/>
+      <c r="C16" s="28" t="s">
+        <v>5</v>
+      </c>
+      <c r="D16" s="30" t="s">
         <v>11</v>
       </c>
-      <c r="N5" s="5"/>
-      <c r="O5" s="5"/>
-      <c r="P5" s="5"/>
-      <c r="Q5" s="18"/>
-    </row>
-    <row r="6" spans="2:17" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B6" s="19"/>
-      <c r="C6" s="20"/>
-      <c r="D6" s="20"/>
-      <c r="E6" s="20"/>
-      <c r="F6" s="20"/>
-      <c r="G6" s="20"/>
-      <c r="H6" s="20"/>
-      <c r="I6" s="20"/>
-      <c r="J6" s="20"/>
-      <c r="K6" s="20"/>
-      <c r="L6" s="20"/>
-      <c r="M6" s="20"/>
-      <c r="N6" s="20"/>
-      <c r="O6" s="20"/>
-      <c r="P6" s="20"/>
-      <c r="Q6" s="21"/>
-    </row>
-    <row r="7" spans="2:17" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="8" spans="2:17" ht="15" thickTop="1" x14ac:dyDescent="0.35">
-      <c r="B8" s="14"/>
-      <c r="C8" s="15"/>
-      <c r="D8" s="15"/>
-      <c r="E8" s="15"/>
-      <c r="F8" s="15"/>
-      <c r="G8" s="15"/>
-      <c r="H8" s="15"/>
-      <c r="I8" s="15"/>
-      <c r="J8" s="15"/>
-      <c r="K8" s="15"/>
-      <c r="L8" s="15"/>
-      <c r="M8" s="15"/>
-      <c r="N8" s="15"/>
-      <c r="O8" s="15"/>
-      <c r="P8" s="15"/>
-      <c r="Q8" s="16"/>
-    </row>
-    <row r="9" spans="2:17" ht="35" thickBot="1" x14ac:dyDescent="0.85">
-      <c r="B9" s="17"/>
-      <c r="C9" s="30" t="s">
-        <v>2</v>
-      </c>
-      <c r="D9" s="30"/>
-      <c r="E9" s="30"/>
-      <c r="F9" s="30"/>
-      <c r="G9" s="7"/>
-      <c r="H9" s="6"/>
-      <c r="I9" s="6"/>
-      <c r="J9" s="6"/>
-      <c r="K9" s="6"/>
-      <c r="L9" s="6"/>
-      <c r="M9" s="6"/>
-      <c r="N9" s="6"/>
-      <c r="O9" s="6"/>
-      <c r="P9" s="6"/>
-      <c r="Q9" s="18"/>
-    </row>
-    <row r="10" spans="2:17" ht="15" thickTop="1" x14ac:dyDescent="0.35">
-      <c r="B10" s="17"/>
-      <c r="C10" s="6"/>
-      <c r="D10" s="6"/>
-      <c r="E10" s="6"/>
-      <c r="F10" s="6"/>
-      <c r="G10" s="6"/>
-      <c r="H10" s="6"/>
-      <c r="I10" s="6"/>
-      <c r="J10" s="6"/>
-      <c r="K10" s="6"/>
-      <c r="L10" s="6"/>
-      <c r="M10" s="6"/>
-      <c r="N10" s="6"/>
-      <c r="O10" s="6"/>
-      <c r="P10" s="6"/>
-      <c r="Q10" s="18"/>
-    </row>
-    <row r="11" spans="2:17" ht="16" x14ac:dyDescent="0.35">
-      <c r="B11" s="17"/>
-      <c r="C11" s="26" t="s">
-        <v>3</v>
-      </c>
-      <c r="D11" s="26"/>
-      <c r="E11" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="F11" s="4"/>
-      <c r="G11" s="4"/>
-      <c r="H11" s="6"/>
-      <c r="I11" s="6"/>
-      <c r="J11" s="6"/>
-      <c r="K11" s="6"/>
-      <c r="L11" s="6"/>
-      <c r="M11" s="6"/>
-      <c r="N11" s="6"/>
-      <c r="O11" s="6"/>
-      <c r="P11" s="6"/>
-      <c r="Q11" s="18"/>
-    </row>
-    <row r="12" spans="2:17" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B12" s="17"/>
-      <c r="C12" s="6"/>
-      <c r="D12" s="6"/>
-      <c r="E12" s="6"/>
-      <c r="F12" s="6"/>
-      <c r="G12" s="6"/>
-      <c r="H12" s="6"/>
-      <c r="I12" s="6"/>
-      <c r="J12" s="6"/>
-      <c r="K12" s="6"/>
-      <c r="L12" s="6"/>
-      <c r="M12" s="6"/>
-      <c r="N12" s="6"/>
-      <c r="O12" s="6"/>
-      <c r="P12" s="6"/>
-      <c r="Q12" s="18"/>
-    </row>
-    <row r="13" spans="2:17" ht="7" customHeight="1" thickTop="1" x14ac:dyDescent="0.35">
-      <c r="B13" s="17"/>
-      <c r="C13" s="8"/>
-      <c r="D13" s="9"/>
-      <c r="E13" s="6"/>
-      <c r="F13" s="6"/>
-      <c r="G13" s="8"/>
-      <c r="H13" s="9"/>
-      <c r="I13" s="6"/>
-      <c r="J13" s="6"/>
-      <c r="K13" s="8"/>
-      <c r="L13" s="9"/>
-      <c r="M13" s="6"/>
-      <c r="N13" s="6"/>
-      <c r="O13" s="8"/>
-      <c r="P13" s="9"/>
-      <c r="Q13" s="18"/>
-    </row>
-    <row r="14" spans="2:17" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B14" s="17"/>
-      <c r="C14" s="27" t="s">
-        <v>4</v>
-      </c>
-      <c r="D14" s="28"/>
-      <c r="E14" s="6"/>
-      <c r="F14" s="6"/>
-      <c r="G14" s="27" t="s">
+      <c r="E16" s="29" t="s">
+        <v>10</v>
+      </c>
+      <c r="F16" s="2"/>
+      <c r="G16" s="28" t="s">
+        <v>5</v>
+      </c>
+      <c r="H16" s="30" t="s">
+        <v>11</v>
+      </c>
+      <c r="I16" s="29" t="s">
+        <v>10</v>
+      </c>
+      <c r="J16" s="2"/>
+      <c r="K16" s="28" t="s">
+        <v>5</v>
+      </c>
+      <c r="L16" s="30" t="s">
+        <v>11</v>
+      </c>
+      <c r="M16" s="29" t="s">
+        <v>10</v>
+      </c>
+      <c r="N16" s="2"/>
+      <c r="O16" s="28" t="s">
+        <v>5</v>
+      </c>
+      <c r="P16" s="30" t="s">
+        <v>11</v>
+      </c>
+      <c r="Q16" s="29" t="s">
+        <v>10</v>
+      </c>
+      <c r="R16" s="17"/>
+    </row>
+    <row r="17" spans="2:18" ht="7" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B17" s="11"/>
+      <c r="C17" s="6"/>
+      <c r="D17" s="27"/>
+      <c r="E17" s="7"/>
+      <c r="F17" s="2"/>
+      <c r="G17" s="6"/>
+      <c r="H17" s="27"/>
+      <c r="I17" s="7"/>
+      <c r="J17" s="2"/>
+      <c r="K17" s="6"/>
+      <c r="L17" s="27"/>
+      <c r="M17" s="7"/>
+      <c r="N17" s="2"/>
+      <c r="O17" s="6"/>
+      <c r="P17" s="27"/>
+      <c r="Q17" s="7"/>
+      <c r="R17" s="12"/>
+    </row>
+    <row r="18" spans="2:18" ht="15" thickTop="1" x14ac:dyDescent="0.35">
+      <c r="B18" s="11"/>
+      <c r="C18" s="2"/>
+      <c r="D18" s="2"/>
+      <c r="E18" s="2"/>
+      <c r="F18" s="2"/>
+      <c r="G18" s="2"/>
+      <c r="H18" s="2"/>
+      <c r="I18" s="2"/>
+      <c r="J18" s="2"/>
+      <c r="K18" s="2"/>
+      <c r="L18" s="2"/>
+      <c r="M18" s="2"/>
+      <c r="N18" s="2"/>
+      <c r="O18" s="2"/>
+      <c r="P18" s="2"/>
+      <c r="Q18" s="2"/>
+      <c r="R18" s="12"/>
+    </row>
+    <row r="19" spans="2:18" x14ac:dyDescent="0.35">
+      <c r="B19" s="11"/>
+      <c r="C19" s="2"/>
+      <c r="D19" s="2"/>
+      <c r="E19" s="2"/>
+      <c r="F19" s="2"/>
+      <c r="G19" s="2"/>
+      <c r="H19" s="2"/>
+      <c r="I19" s="2"/>
+      <c r="J19" s="2"/>
+      <c r="K19" s="2"/>
+      <c r="L19" s="2"/>
+      <c r="M19" s="2"/>
+      <c r="N19" s="23" t="s">
         <v>7</v>
       </c>
-      <c r="H14" s="28"/>
-      <c r="I14" s="6"/>
-      <c r="J14" s="6"/>
-      <c r="K14" s="27" t="s">
-        <v>8</v>
-      </c>
-      <c r="L14" s="28"/>
-      <c r="M14" s="6"/>
-      <c r="N14" s="6"/>
-      <c r="O14" s="27" t="s">
+      <c r="O19" s="23"/>
+      <c r="P19" s="23"/>
+      <c r="Q19" s="23"/>
+      <c r="R19" s="12"/>
+    </row>
+    <row r="20" spans="2:18" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B20" s="13"/>
+      <c r="C20" s="14"/>
+      <c r="D20" s="14"/>
+      <c r="E20" s="14"/>
+      <c r="F20" s="14"/>
+      <c r="G20" s="14"/>
+      <c r="H20" s="14"/>
+      <c r="I20" s="14"/>
+      <c r="J20" s="14"/>
+      <c r="K20" s="14"/>
+      <c r="L20" s="14"/>
+      <c r="M20" s="14"/>
+      <c r="N20" s="14"/>
+      <c r="O20" s="14"/>
+      <c r="P20" s="14"/>
+      <c r="Q20" s="14"/>
+      <c r="R20" s="15"/>
+    </row>
+    <row r="21" spans="2:18" ht="15.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="22" spans="2:18" ht="15" thickTop="1" x14ac:dyDescent="0.35">
+      <c r="B22" s="8"/>
+      <c r="C22" s="9"/>
+      <c r="D22" s="9"/>
+      <c r="E22" s="9"/>
+      <c r="F22" s="9"/>
+      <c r="G22" s="9"/>
+      <c r="H22" s="9"/>
+      <c r="I22" s="9"/>
+      <c r="J22" s="9"/>
+      <c r="K22" s="9"/>
+      <c r="L22" s="9"/>
+      <c r="M22" s="9"/>
+      <c r="N22" s="9"/>
+      <c r="O22" s="9"/>
+      <c r="P22" s="9"/>
+      <c r="Q22" s="9"/>
+      <c r="R22" s="10"/>
+    </row>
+    <row r="23" spans="2:18" ht="35" thickBot="1" x14ac:dyDescent="0.85">
+      <c r="B23" s="11"/>
+      <c r="C23" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="P14" s="28"/>
-      <c r="Q14" s="22"/>
-    </row>
-    <row r="15" spans="2:17" ht="7" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B15" s="17"/>
-      <c r="C15" s="10"/>
-      <c r="D15" s="11"/>
-      <c r="E15" s="6"/>
-      <c r="F15" s="6"/>
-      <c r="G15" s="10"/>
-      <c r="H15" s="11"/>
-      <c r="I15" s="6"/>
-      <c r="J15" s="6"/>
-      <c r="K15" s="10"/>
-      <c r="L15" s="11"/>
-      <c r="M15" s="6"/>
-      <c r="N15" s="6"/>
-      <c r="O15" s="10"/>
-      <c r="P15" s="11"/>
-      <c r="Q15" s="18"/>
-    </row>
-    <row r="16" spans="2:17" ht="32" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B16" s="17"/>
-      <c r="C16" s="29" t="s">
+      <c r="D23" s="20"/>
+      <c r="E23" s="20"/>
+      <c r="F23" s="20"/>
+      <c r="G23" s="3"/>
+      <c r="H23" s="3"/>
+      <c r="I23" s="2"/>
+      <c r="J23" s="2"/>
+      <c r="K23" s="2"/>
+      <c r="L23" s="2"/>
+      <c r="M23" s="2"/>
+      <c r="N23" s="2"/>
+      <c r="O23" s="2"/>
+      <c r="P23" s="2"/>
+      <c r="Q23" s="2"/>
+      <c r="R23" s="12"/>
+    </row>
+    <row r="24" spans="2:18" ht="15" thickTop="1" x14ac:dyDescent="0.35">
+      <c r="B24" s="11"/>
+      <c r="C24" s="2"/>
+      <c r="D24" s="2"/>
+      <c r="E24" s="2"/>
+      <c r="F24" s="2"/>
+      <c r="G24" s="2"/>
+      <c r="H24" s="2"/>
+      <c r="I24" s="2"/>
+      <c r="J24" s="2"/>
+      <c r="K24" s="2"/>
+      <c r="L24" s="2"/>
+      <c r="M24" s="2"/>
+      <c r="N24" s="2"/>
+      <c r="O24" s="2"/>
+      <c r="P24" s="2"/>
+      <c r="Q24" s="2"/>
+      <c r="R24" s="12"/>
+    </row>
+    <row r="25" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B25" s="41" t="s">
+        <v>22</v>
+      </c>
+      <c r="C25" s="35" t="s">
+        <v>16</v>
+      </c>
+      <c r="D25" s="35"/>
+      <c r="E25" s="35"/>
+      <c r="F25"/>
+      <c r="G25" s="35" t="s">
+        <v>17</v>
+      </c>
+      <c r="H25" s="35"/>
+      <c r="I25" s="35"/>
+      <c r="J25"/>
+      <c r="K25" s="35" t="s">
+        <v>18</v>
+      </c>
+      <c r="L25" s="35"/>
+      <c r="M25" s="35"/>
+      <c r="N25"/>
+      <c r="O25" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="P25" s="35"/>
+      <c r="Q25" s="35"/>
+      <c r="R25" s="12"/>
+    </row>
+    <row r="26" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B26" s="41"/>
+      <c r="C26" s="38" t="s">
         <v>5</v>
       </c>
-      <c r="D16" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="E16" s="6"/>
-      <c r="F16" s="6"/>
-      <c r="G16" s="29" t="s">
+      <c r="D26" s="38"/>
+      <c r="E26" s="38"/>
+      <c r="F26" s="36"/>
+      <c r="G26" s="38" t="s">
+        <v>20</v>
+      </c>
+      <c r="H26" s="38"/>
+      <c r="I26" s="38"/>
+      <c r="J26" s="36"/>
+      <c r="K26" s="38" t="s">
+        <v>21</v>
+      </c>
+      <c r="L26" s="38"/>
+      <c r="M26" s="38"/>
+      <c r="N26" s="36"/>
+      <c r="O26" s="38" t="s">
+        <v>21</v>
+      </c>
+      <c r="P26" s="38"/>
+      <c r="Q26" s="38"/>
+      <c r="R26" s="17"/>
+    </row>
+    <row r="27" spans="2:18" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B27" s="43"/>
+      <c r="C27" s="34"/>
+      <c r="D27" s="34"/>
+      <c r="E27" s="34"/>
+      <c r="F27" s="34"/>
+      <c r="G27" s="34"/>
+      <c r="H27" s="34"/>
+      <c r="I27" s="34"/>
+      <c r="J27" s="34"/>
+      <c r="K27" s="34"/>
+      <c r="L27" s="34"/>
+      <c r="M27" s="34"/>
+      <c r="N27" s="34"/>
+      <c r="O27" s="34"/>
+      <c r="P27" s="34"/>
+      <c r="Q27" s="34"/>
+      <c r="R27" s="12"/>
+    </row>
+    <row r="28" spans="2:18" ht="15" thickTop="1" x14ac:dyDescent="0.35">
+      <c r="B28" s="11"/>
+      <c r="C28" s="39"/>
+      <c r="D28" s="39"/>
+      <c r="E28" s="39"/>
+      <c r="F28" s="39"/>
+      <c r="G28" s="39"/>
+      <c r="H28" s="39"/>
+      <c r="I28" s="39"/>
+      <c r="J28" s="39"/>
+      <c r="K28" s="39"/>
+      <c r="L28" s="39"/>
+      <c r="M28" s="39"/>
+      <c r="N28" s="39"/>
+      <c r="O28" s="39"/>
+      <c r="P28" s="39"/>
+      <c r="Q28" s="39"/>
+      <c r="R28" s="12"/>
+    </row>
+    <row r="29" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B29" s="41" t="s">
+        <v>29</v>
+      </c>
+      <c r="C29" s="45"/>
+      <c r="D29" s="35" t="s">
+        <v>30</v>
+      </c>
+      <c r="E29" s="35"/>
+      <c r="F29" s="40"/>
+      <c r="G29" s="48" t="s">
+        <v>31</v>
+      </c>
+      <c r="H29" s="45"/>
+      <c r="I29" s="40"/>
+      <c r="J29" s="46" t="s">
+        <v>32</v>
+      </c>
+      <c r="K29" s="45"/>
+      <c r="L29"/>
+      <c r="M29" s="48" t="s">
+        <v>33</v>
+      </c>
+      <c r="N29" s="46"/>
+      <c r="O29" s="47" t="s">
+        <v>34</v>
+      </c>
+      <c r="P29" s="47"/>
+      <c r="Q29" s="45"/>
+      <c r="R29" s="12"/>
+    </row>
+    <row r="30" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B30" s="41"/>
+      <c r="C30" s="44"/>
+      <c r="D30" s="38" t="s">
         <v>5</v>
       </c>
-      <c r="H16" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="I16" s="6"/>
-      <c r="J16" s="6"/>
-      <c r="K16" s="29" t="s">
+      <c r="E30" s="38"/>
+      <c r="F30" s="36"/>
+      <c r="G30" s="37" t="s">
         <v>5</v>
       </c>
-      <c r="L16" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="M16" s="6"/>
-      <c r="N16" s="6"/>
-      <c r="O16" s="29" t="s">
+      <c r="H30" s="44"/>
+      <c r="I30" s="44"/>
+      <c r="J30" s="37" t="s">
         <v>5</v>
       </c>
-      <c r="P16" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="Q16" s="23"/>
-    </row>
-    <row r="17" spans="2:17" ht="7" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B17" s="17"/>
-      <c r="C17" s="12"/>
-      <c r="D17" s="13"/>
-      <c r="E17" s="6"/>
-      <c r="F17" s="6"/>
-      <c r="G17" s="12"/>
-      <c r="H17" s="13"/>
-      <c r="I17" s="6"/>
-      <c r="J17" s="6"/>
-      <c r="K17" s="12"/>
-      <c r="L17" s="13"/>
-      <c r="M17" s="6"/>
-      <c r="N17" s="6"/>
-      <c r="O17" s="12"/>
-      <c r="P17" s="13"/>
-      <c r="Q17" s="18"/>
-    </row>
-    <row r="18" spans="2:17" ht="15" thickTop="1" x14ac:dyDescent="0.35">
-      <c r="B18" s="17"/>
-      <c r="C18" s="6"/>
-      <c r="D18" s="6"/>
-      <c r="E18" s="6"/>
-      <c r="F18" s="6"/>
-      <c r="G18" s="6"/>
-      <c r="H18" s="6"/>
-      <c r="I18" s="6"/>
-      <c r="J18" s="6"/>
-      <c r="K18" s="6"/>
-      <c r="L18" s="6"/>
-      <c r="M18" s="6"/>
-      <c r="N18" s="6"/>
-      <c r="O18" s="6"/>
-      <c r="P18" s="6"/>
-      <c r="Q18" s="18"/>
-    </row>
-    <row r="19" spans="2:17" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B19" s="19"/>
-      <c r="C19" s="20"/>
-      <c r="D19" s="20"/>
-      <c r="E19" s="20"/>
-      <c r="F19" s="20"/>
-      <c r="G19" s="20"/>
-      <c r="H19" s="20"/>
-      <c r="I19" s="20"/>
-      <c r="J19" s="20"/>
-      <c r="K19" s="20"/>
-      <c r="L19" s="20"/>
-      <c r="M19" s="20"/>
-      <c r="N19" s="20"/>
-      <c r="O19" s="20"/>
-      <c r="P19" s="20"/>
-      <c r="Q19" s="21"/>
-    </row>
-    <row r="20" spans="2:17" ht="15" thickTop="1" x14ac:dyDescent="0.35"/>
-    <row r="23" spans="2:17" x14ac:dyDescent="0.35">
-      <c r="H23" s="1"/>
-      <c r="I23" s="1"/>
-      <c r="J23" s="1"/>
-    </row>
-    <row r="33" s="2" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="34" s="2" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="35" s="2" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="36" s="2" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="37" s="2" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="38" s="2" customFormat="1" x14ac:dyDescent="0.35"/>
+      <c r="K30" s="37"/>
+      <c r="L30" s="44"/>
+      <c r="M30" s="37" t="s">
+        <v>5</v>
+      </c>
+      <c r="N30" s="37"/>
+      <c r="O30" s="38" t="s">
+        <v>5</v>
+      </c>
+      <c r="P30" s="38"/>
+      <c r="Q30" s="44"/>
+      <c r="R30" s="17"/>
+    </row>
+    <row r="31" spans="2:18" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B31" s="43"/>
+      <c r="C31" s="34"/>
+      <c r="D31" s="34"/>
+      <c r="E31" s="34"/>
+      <c r="F31" s="34"/>
+      <c r="G31" s="34"/>
+      <c r="H31" s="34"/>
+      <c r="I31" s="34"/>
+      <c r="J31" s="34"/>
+      <c r="K31" s="34"/>
+      <c r="L31" s="34"/>
+      <c r="M31" s="34"/>
+      <c r="N31" s="34"/>
+      <c r="O31" s="34"/>
+      <c r="P31" s="34"/>
+      <c r="Q31" s="34"/>
+      <c r="R31" s="12"/>
+    </row>
+    <row r="32" spans="2:18" ht="15" thickTop="1" x14ac:dyDescent="0.35">
+      <c r="B32" s="42"/>
+      <c r="C32" s="39"/>
+      <c r="D32" s="39"/>
+      <c r="E32" s="39"/>
+      <c r="F32" s="39"/>
+      <c r="G32" s="39"/>
+      <c r="H32" s="39"/>
+      <c r="I32" s="39"/>
+      <c r="J32" s="39"/>
+      <c r="K32" s="39"/>
+      <c r="L32" s="39"/>
+      <c r="M32" s="39"/>
+      <c r="N32" s="39"/>
+      <c r="O32" s="39"/>
+      <c r="P32" s="39"/>
+      <c r="Q32" s="39"/>
+      <c r="R32" s="12"/>
+    </row>
+    <row r="33" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B33" s="41" t="s">
+        <v>28</v>
+      </c>
+      <c r="C33" s="35" t="s">
+        <v>23</v>
+      </c>
+      <c r="D33" s="35"/>
+      <c r="E33" s="35"/>
+      <c r="F33"/>
+      <c r="G33" s="35" t="s">
+        <v>24</v>
+      </c>
+      <c r="H33" s="35"/>
+      <c r="I33" s="35"/>
+      <c r="J33"/>
+      <c r="K33" s="35" t="s">
+        <v>25</v>
+      </c>
+      <c r="L33" s="35"/>
+      <c r="M33" s="35"/>
+      <c r="N33"/>
+      <c r="O33" s="35" t="s">
+        <v>26</v>
+      </c>
+      <c r="P33" s="35"/>
+      <c r="Q33" s="35"/>
+      <c r="R33" s="12"/>
+    </row>
+    <row r="34" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B34" s="41"/>
+      <c r="C34" s="38" t="s">
+        <v>5</v>
+      </c>
+      <c r="D34" s="38"/>
+      <c r="E34" s="38"/>
+      <c r="F34" s="36"/>
+      <c r="G34" s="38" t="s">
+        <v>27</v>
+      </c>
+      <c r="H34" s="38"/>
+      <c r="I34" s="38"/>
+      <c r="J34" s="36"/>
+      <c r="K34" s="38" t="s">
+        <v>27</v>
+      </c>
+      <c r="L34" s="38"/>
+      <c r="M34" s="38"/>
+      <c r="N34" s="36"/>
+      <c r="O34" s="38" t="s">
+        <v>27</v>
+      </c>
+      <c r="P34" s="38"/>
+      <c r="Q34" s="38"/>
+      <c r="R34" s="17"/>
+    </row>
+    <row r="35" spans="2:18" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B35" s="42"/>
+      <c r="C35" s="34"/>
+      <c r="D35" s="34"/>
+      <c r="E35" s="34"/>
+      <c r="F35" s="34"/>
+      <c r="G35" s="34"/>
+      <c r="H35" s="34"/>
+      <c r="I35" s="34"/>
+      <c r="J35" s="34"/>
+      <c r="K35" s="34"/>
+      <c r="L35" s="34"/>
+      <c r="M35" s="34"/>
+      <c r="N35" s="34"/>
+      <c r="O35" s="34"/>
+      <c r="P35" s="34"/>
+      <c r="Q35" s="34"/>
+      <c r="R35" s="12"/>
+    </row>
+    <row r="36" spans="2:18" ht="15" thickTop="1" x14ac:dyDescent="0.35">
+      <c r="B36" s="42"/>
+      <c r="C36" s="39"/>
+      <c r="D36" s="39"/>
+      <c r="E36" s="39"/>
+      <c r="F36" s="39"/>
+      <c r="G36" s="39"/>
+      <c r="H36" s="39"/>
+      <c r="I36" s="39"/>
+      <c r="J36" s="39"/>
+      <c r="K36" s="39"/>
+      <c r="L36" s="39"/>
+      <c r="M36" s="39"/>
+      <c r="N36" s="39"/>
+      <c r="O36" s="39"/>
+      <c r="P36" s="39"/>
+      <c r="Q36" s="39"/>
+      <c r="R36" s="12"/>
+    </row>
+    <row r="37" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B37" s="41" t="s">
+        <v>35</v>
+      </c>
+      <c r="C37" s="35" t="s">
+        <v>37</v>
+      </c>
+      <c r="D37" s="35"/>
+      <c r="E37" s="35"/>
+      <c r="F37"/>
+      <c r="G37" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="H37" s="35"/>
+      <c r="I37" s="35"/>
+      <c r="J37"/>
+      <c r="K37" s="35" t="s">
+        <v>40</v>
+      </c>
+      <c r="L37" s="35"/>
+      <c r="M37" s="35"/>
+      <c r="N37"/>
+      <c r="O37" s="35" t="s">
+        <v>41</v>
+      </c>
+      <c r="P37" s="35"/>
+      <c r="Q37" s="35"/>
+      <c r="R37" s="12"/>
+    </row>
+    <row r="38" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B38" s="41"/>
+      <c r="C38" s="38" t="s">
+        <v>39</v>
+      </c>
+      <c r="D38" s="38"/>
+      <c r="E38" s="38"/>
+      <c r="F38" s="36"/>
+      <c r="G38" s="38" t="s">
+        <v>36</v>
+      </c>
+      <c r="H38" s="38"/>
+      <c r="I38" s="38"/>
+      <c r="J38" s="36"/>
+      <c r="K38" s="38" t="s">
+        <v>27</v>
+      </c>
+      <c r="L38" s="38"/>
+      <c r="M38" s="38"/>
+      <c r="N38" s="36"/>
+      <c r="O38" s="38" t="s">
+        <v>27</v>
+      </c>
+      <c r="P38" s="38"/>
+      <c r="Q38" s="38"/>
+      <c r="R38" s="17"/>
+    </row>
+    <row r="39" spans="2:18" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B39" s="42"/>
+      <c r="C39" s="34"/>
+      <c r="D39" s="34"/>
+      <c r="E39" s="34"/>
+      <c r="F39" s="34"/>
+      <c r="G39" s="34"/>
+      <c r="H39" s="34"/>
+      <c r="I39" s="34"/>
+      <c r="J39" s="34"/>
+      <c r="K39" s="34"/>
+      <c r="L39" s="34"/>
+      <c r="M39" s="34"/>
+      <c r="N39" s="34"/>
+      <c r="O39" s="34"/>
+      <c r="P39" s="34"/>
+      <c r="Q39" s="34"/>
+      <c r="R39" s="12"/>
+    </row>
+    <row r="40" spans="2:18" ht="16.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.35">
+      <c r="B40" s="11"/>
+      <c r="C40" s="2"/>
+      <c r="D40" s="2"/>
+      <c r="E40" s="2"/>
+      <c r="F40" s="2"/>
+      <c r="G40" s="2"/>
+      <c r="H40" s="2"/>
+      <c r="I40" s="2"/>
+      <c r="J40" s="2"/>
+      <c r="K40" s="2"/>
+      <c r="L40" s="2"/>
+      <c r="M40" s="2"/>
+      <c r="N40" s="2"/>
+      <c r="O40" s="2"/>
+      <c r="P40" s="2"/>
+      <c r="Q40" s="2"/>
+      <c r="R40" s="12"/>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.35">
+      <c r="B41" s="11"/>
+      <c r="C41" s="2"/>
+      <c r="D41" s="2"/>
+      <c r="E41" s="2"/>
+      <c r="F41" s="2"/>
+      <c r="G41" s="2"/>
+      <c r="H41" s="2"/>
+      <c r="I41" s="2"/>
+      <c r="J41" s="2"/>
+      <c r="K41" s="2"/>
+      <c r="L41" s="2"/>
+      <c r="M41" s="2"/>
+      <c r="N41" s="23" t="s">
+        <v>7</v>
+      </c>
+      <c r="O41" s="23"/>
+      <c r="P41" s="23"/>
+      <c r="Q41" s="23"/>
+      <c r="R41" s="12"/>
+    </row>
+    <row r="42" spans="2:18" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B42" s="13"/>
+      <c r="C42" s="14"/>
+      <c r="D42" s="14"/>
+      <c r="E42" s="14"/>
+      <c r="F42" s="14"/>
+      <c r="G42" s="14"/>
+      <c r="H42" s="14"/>
+      <c r="I42" s="14"/>
+      <c r="J42" s="14"/>
+      <c r="K42" s="14"/>
+      <c r="L42" s="14"/>
+      <c r="M42" s="14"/>
+      <c r="N42" s="14"/>
+      <c r="O42" s="14"/>
+      <c r="P42" s="14"/>
+      <c r="Q42" s="14"/>
+      <c r="R42" s="15"/>
+    </row>
+    <row r="43" spans="2:18" ht="15" thickTop="1" x14ac:dyDescent="0.35"/>
   </sheetData>
-  <mergeCells count="7">
-    <mergeCell ref="O14:P14"/>
-    <mergeCell ref="M5:P5"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="E11:G11"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="G14:H14"/>
-    <mergeCell ref="K14:L14"/>
+  <mergeCells count="43">
+    <mergeCell ref="N19:Q19"/>
+    <mergeCell ref="N41:Q41"/>
+    <mergeCell ref="O30:P30"/>
+    <mergeCell ref="B37:B38"/>
+    <mergeCell ref="C37:E37"/>
+    <mergeCell ref="G37:I37"/>
+    <mergeCell ref="K37:M37"/>
+    <mergeCell ref="O37:Q37"/>
+    <mergeCell ref="C38:E38"/>
+    <mergeCell ref="G38:I38"/>
+    <mergeCell ref="K38:M38"/>
+    <mergeCell ref="O38:Q38"/>
+    <mergeCell ref="B29:B30"/>
+    <mergeCell ref="D29:E29"/>
+    <mergeCell ref="D30:E30"/>
+    <mergeCell ref="O29:P29"/>
+    <mergeCell ref="B25:B26"/>
+    <mergeCell ref="B33:B34"/>
+    <mergeCell ref="O33:Q33"/>
+    <mergeCell ref="C34:E34"/>
+    <mergeCell ref="G34:I34"/>
+    <mergeCell ref="K34:M34"/>
+    <mergeCell ref="O34:Q34"/>
+    <mergeCell ref="O26:Q26"/>
+    <mergeCell ref="C25:E25"/>
+    <mergeCell ref="G25:I25"/>
+    <mergeCell ref="K25:M25"/>
+    <mergeCell ref="O25:Q25"/>
+    <mergeCell ref="C26:E26"/>
+    <mergeCell ref="G26:I26"/>
+    <mergeCell ref="K26:M26"/>
+    <mergeCell ref="C33:E33"/>
+    <mergeCell ref="G33:I33"/>
+    <mergeCell ref="K33:M33"/>
+    <mergeCell ref="N5:Q5"/>
+    <mergeCell ref="C11:E11"/>
+    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="K15:M15"/>
+    <mergeCell ref="C14:E15"/>
+    <mergeCell ref="G14:I14"/>
+    <mergeCell ref="K14:M14"/>
+    <mergeCell ref="O14:Q15"/>
+    <mergeCell ref="F11:H11"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
